--- a/docs/reports/內在價值報告_20260918.xlsx
+++ b/docs/reports/內在價值報告_20260918.xlsx
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>425.19</v>
+        <v>431.57</v>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
@@ -1438,22 +1438,22 @@
       </c>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="4" t="n">
-        <v>6265.3154</v>
+        <v>6265.31</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>539.3167</v>
+        <v>539.2962</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>5285.4917</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>-93.2</v>
+        <v>-93.09999999999999</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>25</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>4698.9865</v>
+        <v>4698.9825</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AE7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AF7" s="3" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>510.14</v>
+        <v>508.34</v>
       </c>
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="AE11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AF11" s="3" t="inlineStr">
@@ -3479,7 +3479,7 @@
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>269.25</v>
+        <v>268.515</v>
       </c>
       <c r="E24" s="8" t="inlineStr"/>
       <c r="F24" s="7" t="inlineStr">
@@ -3494,22 +3494,22 @@
       </c>
       <c r="H24" s="8" t="inlineStr"/>
       <c r="I24" s="9" t="n">
-        <v>480.8054</v>
+        <v>480.806</v>
       </c>
       <c r="J24" s="9" t="n">
         <v>9.3416</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>17.7683</v>
+        <v>17.7685</v>
       </c>
       <c r="L24" s="10" t="n">
-        <v>-44</v>
+        <v>-44.2</v>
       </c>
       <c r="M24" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>360.604</v>
+        <v>360.6045</v>
       </c>
       <c r="O24" s="7" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="AE24" s="7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AF24" s="8" t="inlineStr">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="D34" s="14" t="n">
-        <v>377.275</v>
+        <v>373.955</v>
       </c>
       <c r="E34" s="13" t="inlineStr"/>
       <c r="F34" s="12" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="H34" s="13" t="inlineStr"/>
       <c r="I34" s="14" t="n">
-        <v>369.4246</v>
+        <v>369.4252</v>
       </c>
       <c r="J34" s="14" t="n">
         <v>64.4277</v>
@@ -4711,13 +4711,13 @@
         <v>314.2098</v>
       </c>
       <c r="L34" s="15" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="M34" s="15" t="n">
         <v>25</v>
       </c>
       <c r="N34" s="14" t="n">
-        <v>277.0684</v>
+        <v>277.0689</v>
       </c>
       <c r="O34" s="12" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="AE34" s="12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AF34" s="13" t="inlineStr">
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="D44" s="24" t="n">
-        <v>218.879</v>
+        <v>219.54</v>
       </c>
       <c r="E44" s="23" t="inlineStr"/>
       <c r="F44" s="22" t="inlineStr">
@@ -5915,13 +5915,13 @@
         <v>45.7474</v>
       </c>
       <c r="J44" s="24" t="n">
-        <v>6.8364</v>
+        <v>6.8363</v>
       </c>
       <c r="K44" s="24" t="n">
         <v>31.5866</v>
       </c>
       <c r="L44" s="25" t="n">
-        <v>378.5</v>
+        <v>379.9</v>
       </c>
       <c r="M44" s="25" t="n">
         <v>25</v>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="AE44" s="22" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AF44" s="23" t="inlineStr">
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="D48" s="24" t="n">
-        <v>332.29</v>
+        <v>334.815</v>
       </c>
       <c r="E48" s="23" t="inlineStr"/>
       <c r="F48" s="22" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="H48" s="23" t="inlineStr"/>
       <c r="I48" s="24" t="n">
-        <v>49.1606</v>
+        <v>49.1605</v>
       </c>
       <c r="J48" s="24" t="n">
         <v>9.446</v>
@@ -6405,7 +6405,7 @@
         <v>34.7808</v>
       </c>
       <c r="L48" s="25" t="n">
-        <v>575.9</v>
+        <v>581.1</v>
       </c>
       <c r="M48" s="25" t="n">
         <v>25</v>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="AE48" s="22" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AF48" s="23" t="inlineStr">
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="D49" s="24" t="n">
-        <v>174.765</v>
+        <v>167.445</v>
       </c>
       <c r="E49" s="23" t="inlineStr"/>
       <c r="F49" s="22" t="inlineStr">
@@ -6518,16 +6518,16 @@
       </c>
       <c r="H49" s="23" t="inlineStr"/>
       <c r="I49" s="24" t="n">
-        <v>21.4773</v>
+        <v>21.4774</v>
       </c>
       <c r="J49" s="24" t="n">
         <v>4.7985</v>
       </c>
       <c r="K49" s="24" t="n">
-        <v>5.0402</v>
+        <v>5.0403</v>
       </c>
       <c r="L49" s="25" t="n">
-        <v>713.7</v>
+        <v>679.6</v>
       </c>
       <c r="M49" s="25" t="n">
         <v>25</v>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="AE49" s="22" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AF49" s="23" t="inlineStr">
@@ -6623,7 +6623,7 @@
         </is>
       </c>
       <c r="D50" s="24" t="n">
-        <v>495.94</v>
+        <v>493.811</v>
       </c>
       <c r="E50" s="23" t="inlineStr"/>
       <c r="F50" s="22" t="inlineStr">
@@ -6647,7 +6647,7 @@
         <v>86.59699999999999</v>
       </c>
       <c r="L50" s="25" t="n">
-        <v>507.2</v>
+        <v>504.6</v>
       </c>
       <c r="M50" s="25" t="n">
         <v>25</v>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="AE50" s="22" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AF50" s="23" t="inlineStr">
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="D53" s="24" t="n">
-        <v>1143.93</v>
+        <v>1146.22</v>
       </c>
       <c r="E53" s="23" t="inlineStr"/>
       <c r="F53" s="22" t="inlineStr">
@@ -7000,22 +7000,22 @@
       </c>
       <c r="H53" s="23" t="inlineStr"/>
       <c r="I53" s="24" t="n">
-        <v>544.7392</v>
+        <v>544.7381</v>
       </c>
       <c r="J53" s="24" t="n">
-        <v>58.849</v>
+        <v>58.8487</v>
       </c>
       <c r="K53" s="24" t="n">
         <v>202.834</v>
       </c>
       <c r="L53" s="25" t="n">
-        <v>110</v>
+        <v>110.4</v>
       </c>
       <c r="M53" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N53" s="24" t="n">
-        <v>408.5544</v>
+        <v>408.5536</v>
       </c>
       <c r="O53" s="22" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AE53" s="22" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AF53" s="23" t="inlineStr">
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="D54" s="24" t="n">
-        <v>369.365</v>
+        <v>369.03</v>
       </c>
       <c r="E54" s="23" t="inlineStr"/>
       <c r="F54" s="22" t="inlineStr">
@@ -7131,7 +7131,7 @@
         <v>61.9902</v>
       </c>
       <c r="L54" s="25" t="n">
-        <v>580.7</v>
+        <v>580.1</v>
       </c>
       <c r="M54" s="25" t="n">
         <v>25</v>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="AE54" s="22" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AF54" s="23" t="inlineStr">
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="D55" s="24" t="n">
-        <v>252.07</v>
+        <v>253.56</v>
       </c>
       <c r="E55" s="23" t="inlineStr"/>
       <c r="F55" s="22" t="inlineStr">
@@ -7253,7 +7253,7 @@
         <v>487.2973</v>
       </c>
       <c r="L55" s="25" t="n">
-        <v>135.4</v>
+        <v>136.8</v>
       </c>
       <c r="M55" s="25" t="n">
         <v>25</v>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="AE55" s="22" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AF55" s="23" t="inlineStr">
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="D56" s="24" t="n">
-        <v>346.365</v>
+        <v>350.165</v>
       </c>
       <c r="E56" s="23" t="inlineStr"/>
       <c r="F56" s="22" t="inlineStr">
@@ -7375,7 +7375,7 @@
         <v>15.3128</v>
       </c>
       <c r="L56" s="25" t="n">
-        <v>451</v>
+        <v>457.1</v>
       </c>
       <c r="M56" s="25" t="n">
         <v>25</v>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="AE56" s="22" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AF56" s="23" t="inlineStr">
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="D57" s="24" t="n">
-        <v>33.21</v>
+        <v>32.975</v>
       </c>
       <c r="E57" s="23" t="inlineStr"/>
       <c r="F57" s="22" t="inlineStr">
@@ -7497,7 +7497,7 @@
         <v>5.2053</v>
       </c>
       <c r="L57" s="25" t="n">
-        <v>661.4</v>
+        <v>656</v>
       </c>
       <c r="M57" s="25" t="n">
         <v>25</v>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="AE57" s="22" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AF57" s="23" t="inlineStr">
@@ -7595,7 +7595,7 @@
         </is>
       </c>
       <c r="D58" s="24" t="n">
-        <v>106.36</v>
+        <v>107.11</v>
       </c>
       <c r="E58" s="23" t="inlineStr"/>
       <c r="F58" s="22" t="inlineStr">
@@ -7619,7 +7619,7 @@
         <v>28.2934</v>
       </c>
       <c r="L58" s="25" t="n">
-        <v>799</v>
+        <v>805.3</v>
       </c>
       <c r="M58" s="25" t="n">
         <v>25</v>
@@ -7691,7 +7691,7 @@
       </c>
       <c r="AE58" s="22" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AF58" s="23" t="inlineStr">
@@ -7717,7 +7717,7 @@
         </is>
       </c>
       <c r="D59" s="24" t="n">
-        <v>280.37</v>
+        <v>283.66</v>
       </c>
       <c r="E59" s="23" t="inlineStr"/>
       <c r="F59" s="22" t="inlineStr">
@@ -7741,7 +7741,7 @@
         <v>8.8208</v>
       </c>
       <c r="L59" s="25" t="n">
-        <v>939.7</v>
+        <v>951.9</v>
       </c>
       <c r="M59" s="25" t="n">
         <v>25</v>
@@ -7813,7 +7813,7 @@
       </c>
       <c r="AE59" s="22" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AF59" s="23" t="inlineStr">
@@ -7839,7 +7839,7 @@
         </is>
       </c>
       <c r="D60" s="24" t="n">
-        <v>87.66500000000001</v>
+        <v>87.78</v>
       </c>
       <c r="E60" s="23" t="inlineStr"/>
       <c r="F60" s="22" t="inlineStr">
@@ -7863,7 +7863,7 @@
         <v>11.4611</v>
       </c>
       <c r="L60" s="25" t="n">
-        <v>524</v>
+        <v>524.8</v>
       </c>
       <c r="M60" s="25" t="n">
         <v>25</v>
@@ -7935,7 +7935,7 @@
       </c>
       <c r="AE60" s="22" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AF60" s="23" t="inlineStr">
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="D61" s="24" t="n">
-        <v>146.64</v>
+        <v>146.33</v>
       </c>
       <c r="E61" s="23" t="inlineStr"/>
       <c r="F61" s="22" t="inlineStr">
@@ -7985,7 +7985,7 @@
         <v>13.4653</v>
       </c>
       <c r="L61" s="25" t="n">
-        <v>625.1</v>
+        <v>623.6</v>
       </c>
       <c r="M61" s="25" t="n">
         <v>25</v>
@@ -8057,7 +8057,7 @@
       </c>
       <c r="AE61" s="22" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AF61" s="23" t="inlineStr">
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="D66" s="24" t="n">
-        <v>365</v>
+        <v>365.1</v>
       </c>
       <c r="E66" s="23" t="inlineStr"/>
       <c r="F66" s="22" t="inlineStr">
@@ -8595,7 +8595,7 @@
         <v>4.6574</v>
       </c>
       <c r="L66" s="25" t="n">
-        <v>7959.5</v>
+        <v>7961.7</v>
       </c>
       <c r="M66" s="25" t="n">
         <v>25</v>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="AE66" s="22" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AF66" s="23" t="inlineStr">
@@ -9053,7 +9053,7 @@
         </is>
       </c>
       <c r="D70" s="29" t="n">
-        <v>128.7</v>
+        <v>147.92</v>
       </c>
       <c r="E70" s="28" t="inlineStr"/>
       <c r="F70" s="27" t="inlineStr">
@@ -9081,7 +9081,7 @@
         <v>21296.5965</v>
       </c>
       <c r="L70" s="30" t="n">
-        <v>-99.40000000000001</v>
+        <v>-99.3</v>
       </c>
       <c r="M70" s="30" t="n">
         <v>25</v>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="AE70" s="27" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AF70" s="28" t="inlineStr">
@@ -12238,10 +12238,10 @@
         </is>
       </c>
       <c r="C52" s="34" t="n">
-        <v>332.29</v>
+        <v>334.815</v>
       </c>
       <c r="D52" s="34" t="n">
-        <v>49.1606</v>
+        <v>49.1605</v>
       </c>
       <c r="E52" s="34" t="n">
         <v>9.446</v>
@@ -12252,10 +12252,10 @@
       <c r="G52" s="34" t="inlineStr"/>
       <c r="H52" s="34" t="inlineStr"/>
       <c r="I52" s="34" t="n">
-        <v>8.899699999999999</v>
+        <v>8.8994</v>
       </c>
       <c r="J52" s="34" t="n">
-        <v>12.4165</v>
+        <v>12.4164</v>
       </c>
       <c r="K52" s="34" t="n">
         <v>494.7644</v>
@@ -12293,7 +12293,7 @@
         </is>
       </c>
       <c r="C53" s="34" t="n">
-        <v>252.07</v>
+        <v>253.56</v>
       </c>
       <c r="D53" s="34" t="n">
         <v>107.0856</v>
@@ -12344,7 +12344,7 @@
         </is>
       </c>
       <c r="C54" s="34" t="n">
-        <v>510.14</v>
+        <v>508.34</v>
       </c>
       <c r="D54" s="34" t="n">
         <v>1600617.8442</v>
@@ -12395,7 +12395,7 @@
         </is>
       </c>
       <c r="C55" s="34" t="n">
-        <v>280.37</v>
+        <v>283.66</v>
       </c>
       <c r="D55" s="34" t="n">
         <v>26.9669</v>
@@ -12450,10 +12450,10 @@
         </is>
       </c>
       <c r="C56" s="34" t="n">
-        <v>174.765</v>
+        <v>167.445</v>
       </c>
       <c r="D56" s="34" t="n">
-        <v>21.4773</v>
+        <v>21.4774</v>
       </c>
       <c r="E56" s="34" t="n">
         <v>3.6112</v>
@@ -12464,7 +12464,7 @@
       <c r="G56" s="34" t="inlineStr"/>
       <c r="H56" s="34" t="inlineStr"/>
       <c r="I56" s="34" t="n">
-        <v>5.0402</v>
+        <v>5.0403</v>
       </c>
       <c r="J56" s="34" t="inlineStr"/>
       <c r="K56" s="34" t="n">
@@ -12503,7 +12503,7 @@
         </is>
       </c>
       <c r="C57" s="34" t="n">
-        <v>346.365</v>
+        <v>350.165</v>
       </c>
       <c r="D57" s="34" t="n">
         <v>62.856</v>
@@ -12560,10 +12560,10 @@
         </is>
       </c>
       <c r="C58" s="34" t="n">
-        <v>269.25</v>
+        <v>268.515</v>
       </c>
       <c r="D58" s="34" t="n">
-        <v>480.8054</v>
+        <v>480.806</v>
       </c>
       <c r="E58" s="34" t="n">
         <v>9.3416</v>
@@ -12574,10 +12574,10 @@
       <c r="G58" s="34" t="inlineStr"/>
       <c r="H58" s="34" t="inlineStr"/>
       <c r="I58" s="34" t="n">
-        <v>15.4514</v>
+        <v>15.4533</v>
       </c>
       <c r="J58" s="34" t="n">
-        <v>17.7683</v>
+        <v>17.7685</v>
       </c>
       <c r="K58" s="34" t="n">
         <v>6466.5299</v>
@@ -12615,7 +12615,7 @@
         </is>
       </c>
       <c r="C59" s="34" t="n">
-        <v>87.66500000000001</v>
+        <v>87.78</v>
       </c>
       <c r="D59" s="34" t="n">
         <v>14.0496</v>
@@ -12668,10 +12668,10 @@
         </is>
       </c>
       <c r="C60" s="34" t="n">
-        <v>1143.93</v>
+        <v>1146.22</v>
       </c>
       <c r="D60" s="34" t="n">
-        <v>544.7392</v>
+        <v>544.7381</v>
       </c>
       <c r="E60" s="34" t="n">
         <v>83.318</v>
@@ -12682,10 +12682,10 @@
       <c r="G60" s="34" t="inlineStr"/>
       <c r="H60" s="34" t="inlineStr"/>
       <c r="I60" s="34" t="n">
-        <v>15.5354</v>
+        <v>15.5319</v>
       </c>
       <c r="J60" s="34" t="n">
-        <v>58.849</v>
+        <v>58.8487</v>
       </c>
       <c r="K60" s="34" t="n">
         <v>6600.4801</v>
@@ -12723,7 +12723,7 @@
         </is>
       </c>
       <c r="C61" s="34" t="n">
-        <v>495.94</v>
+        <v>493.811</v>
       </c>
       <c r="D61" s="34" t="n">
         <v>81.6729</v>
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="C62" s="34" t="n">
-        <v>128.7</v>
+        <v>147.92</v>
       </c>
       <c r="D62" s="34" t="n">
         <v>21296.5965</v>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="L62" s="34" t="inlineStr"/>
       <c r="M62" s="34" t="n">
-        <v>9.380000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="N62" s="34" t="n">
         <v>10.15</v>
@@ -12825,7 +12825,7 @@
         </is>
       </c>
       <c r="C63" s="34" t="n">
-        <v>218.879</v>
+        <v>219.54</v>
       </c>
       <c r="D63" s="34" t="n">
         <v>45.7474</v>
@@ -12841,7 +12841,7 @@
       </c>
       <c r="H63" s="34" t="inlineStr"/>
       <c r="I63" s="34" t="n">
-        <v>6.8364</v>
+        <v>6.8363</v>
       </c>
       <c r="J63" s="34" t="n">
         <v>15.1803</v>
@@ -12882,7 +12882,7 @@
         </is>
       </c>
       <c r="C64" s="34" t="n">
-        <v>146.64</v>
+        <v>146.33</v>
       </c>
       <c r="D64" s="34" t="n">
         <v>20.2227</v>
@@ -12937,7 +12937,7 @@
         </is>
       </c>
       <c r="C65" s="34" t="n">
-        <v>33.21</v>
+        <v>32.975</v>
       </c>
       <c r="D65" s="34" t="n">
         <v>4.3617</v>
@@ -12992,7 +12992,7 @@
         </is>
       </c>
       <c r="C66" s="34" t="n">
-        <v>365</v>
+        <v>365.1</v>
       </c>
       <c r="D66" s="34" t="n">
         <v>4.5288</v>
@@ -13049,10 +13049,10 @@
         </is>
       </c>
       <c r="C67" s="34" t="n">
-        <v>425.19</v>
+        <v>431.57</v>
       </c>
       <c r="D67" s="34" t="n">
-        <v>6265.3154</v>
+        <v>6265.31</v>
       </c>
       <c r="E67" s="34" t="n">
         <v>1397.4929</v>
@@ -13065,10 +13065,10 @@
       </c>
       <c r="H67" s="34" t="inlineStr"/>
       <c r="I67" s="34" t="n">
-        <v>539.3167</v>
+        <v>539.2962</v>
       </c>
       <c r="J67" s="34" t="n">
-        <v>905.7893</v>
+        <v>905.7868999999999</v>
       </c>
       <c r="K67" s="34" t="n">
         <v>70736.5186</v>
@@ -13106,10 +13106,10 @@
         </is>
       </c>
       <c r="C68" s="34" t="n">
-        <v>377.275</v>
+        <v>373.955</v>
       </c>
       <c r="D68" s="34" t="n">
-        <v>369.4246</v>
+        <v>369.4252</v>
       </c>
       <c r="E68" s="34" t="n">
         <v>64.4277</v>
@@ -13120,7 +13120,7 @@
       <c r="G68" s="34" t="inlineStr"/>
       <c r="H68" s="34" t="inlineStr"/>
       <c r="I68" s="34" t="n">
-        <v>4.9383</v>
+        <v>4.9397</v>
       </c>
       <c r="J68" s="34" t="inlineStr"/>
       <c r="K68" s="34" t="n">
@@ -13159,7 +13159,7 @@
         </is>
       </c>
       <c r="C69" s="34" t="n">
-        <v>369.365</v>
+        <v>369.03</v>
       </c>
       <c r="D69" s="34" t="n">
         <v>54.2597</v>
@@ -13214,7 +13214,7 @@
         </is>
       </c>
       <c r="C70" s="34" t="n">
-        <v>106.36</v>
+        <v>107.11</v>
       </c>
       <c r="D70" s="34" t="n">
         <v>11.8315</v>
@@ -15646,7 +15646,7 @@
         </is>
       </c>
       <c r="C52" s="24" t="n">
-        <v>332.29</v>
+        <v>334.815</v>
       </c>
       <c r="D52" s="22" t="inlineStr">
         <is>
@@ -15654,19 +15654,19 @@
         </is>
       </c>
       <c r="E52" s="24" t="n">
-        <v>24.5803</v>
+        <v>24.5802</v>
       </c>
       <c r="F52" s="24" t="n">
         <v>36.8704</v>
       </c>
       <c r="G52" s="24" t="n">
-        <v>56.5346</v>
+        <v>56.5345</v>
       </c>
       <c r="H52" s="24" t="n">
-        <v>73.74079999999999</v>
+        <v>73.7407</v>
       </c>
       <c r="I52" s="24" t="n">
-        <v>73.74079999999999</v>
+        <v>73.7407</v>
       </c>
       <c r="J52" s="26" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         </is>
       </c>
       <c r="K52" s="24" t="n">
-        <v>6.7593</v>
+        <v>6.8107</v>
       </c>
       <c r="L52" s="24" t="n">
         <v>36.8704</v>
@@ -15692,7 +15692,7 @@
         </is>
       </c>
       <c r="C53" s="24" t="n">
-        <v>252.07</v>
+        <v>253.56</v>
       </c>
       <c r="D53" s="22" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         </is>
       </c>
       <c r="K53" s="24" t="n">
-        <v>2.3539</v>
+        <v>2.3678</v>
       </c>
       <c r="L53" s="24" t="n">
         <v>80.3142</v>
@@ -15738,7 +15738,7 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>510.14</v>
+        <v>508.34</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         </is>
       </c>
       <c r="C55" s="24" t="n">
-        <v>280.37</v>
+        <v>283.66</v>
       </c>
       <c r="D55" s="22" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         </is>
       </c>
       <c r="K55" s="24" t="n">
-        <v>10.3968</v>
+        <v>10.5188</v>
       </c>
       <c r="L55" s="24" t="n">
         <v>20.2252</v>
@@ -15830,7 +15830,7 @@
         </is>
       </c>
       <c r="C56" s="24" t="n">
-        <v>174.765</v>
+        <v>167.445</v>
       </c>
       <c r="D56" s="22" t="inlineStr">
         <is>
@@ -15844,13 +15844,13 @@
         <v>16.108</v>
       </c>
       <c r="G56" s="24" t="n">
-        <v>24.6989</v>
+        <v>24.699</v>
       </c>
       <c r="H56" s="24" t="n">
-        <v>32.216</v>
+        <v>32.2161</v>
       </c>
       <c r="I56" s="24" t="n">
-        <v>32.216</v>
+        <v>32.2161</v>
       </c>
       <c r="J56" s="26" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         </is>
       </c>
       <c r="K56" s="24" t="n">
-        <v>8.1372</v>
+        <v>7.7963</v>
       </c>
       <c r="L56" s="24" t="n">
         <v>16.108</v>
@@ -15876,7 +15876,7 @@
         </is>
       </c>
       <c r="C57" s="24" t="n">
-        <v>346.365</v>
+        <v>350.165</v>
       </c>
       <c r="D57" s="22" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         </is>
       </c>
       <c r="K57" s="24" t="n">
-        <v>5.5105</v>
+        <v>5.5709</v>
       </c>
       <c r="L57" s="24" t="n">
         <v>47.142</v>
@@ -15922,7 +15922,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>269.25</v>
+        <v>268.515</v>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
@@ -15930,19 +15930,19 @@
         </is>
       </c>
       <c r="E58" s="9" t="n">
-        <v>240.4027</v>
+        <v>240.403</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>360.604</v>
+        <v>360.6045</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>552.9262</v>
+        <v>552.9269</v>
       </c>
       <c r="H58" s="9" t="n">
-        <v>721.2080999999999</v>
+        <v>721.2089999999999</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>721.2080999999999</v>
+        <v>721.2089999999999</v>
       </c>
       <c r="J58" s="11" t="inlineStr">
         <is>
@@ -15950,10 +15950,10 @@
         </is>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5585</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>360.604</v>
+        <v>360.6045</v>
       </c>
     </row>
     <row r="59">
@@ -15968,7 +15968,7 @@
         </is>
       </c>
       <c r="C59" s="24" t="n">
-        <v>87.66500000000001</v>
+        <v>87.78</v>
       </c>
       <c r="D59" s="22" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
         </is>
       </c>
       <c r="K59" s="24" t="n">
-        <v>6.2397</v>
+        <v>6.2479</v>
       </c>
       <c r="L59" s="24" t="n">
         <v>10.5372</v>
@@ -16014,7 +16014,7 @@
         </is>
       </c>
       <c r="C60" s="24" t="n">
-        <v>1143.93</v>
+        <v>1146.22</v>
       </c>
       <c r="D60" s="22" t="inlineStr">
         <is>
@@ -16022,19 +16022,19 @@
         </is>
       </c>
       <c r="E60" s="24" t="n">
-        <v>272.3696</v>
+        <v>272.3691</v>
       </c>
       <c r="F60" s="24" t="n">
-        <v>408.5544</v>
+        <v>408.5536</v>
       </c>
       <c r="G60" s="24" t="n">
-        <v>626.4501</v>
+        <v>626.4488</v>
       </c>
       <c r="H60" s="24" t="n">
-        <v>817.1088</v>
+        <v>817.1072</v>
       </c>
       <c r="I60" s="24" t="n">
-        <v>817.1088</v>
+        <v>817.1072</v>
       </c>
       <c r="J60" s="26" t="inlineStr">
         <is>
@@ -16042,10 +16042,10 @@
         </is>
       </c>
       <c r="K60" s="24" t="n">
-        <v>2.1</v>
+        <v>2.1042</v>
       </c>
       <c r="L60" s="24" t="n">
-        <v>408.5544</v>
+        <v>408.5536</v>
       </c>
     </row>
     <row r="61">
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="C61" s="24" t="n">
-        <v>495.94</v>
+        <v>493.811</v>
       </c>
       <c r="D61" s="22" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         </is>
       </c>
       <c r="K61" s="24" t="n">
-        <v>6.0723</v>
+        <v>6.0462</v>
       </c>
       <c r="L61" s="24" t="n">
         <v>61.2547</v>
@@ -16106,7 +16106,7 @@
         </is>
       </c>
       <c r="C62" s="29" t="n">
-        <v>128.7</v>
+        <v>147.92</v>
       </c>
       <c r="D62" s="27" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         </is>
       </c>
       <c r="K62" s="29" t="n">
-        <v>0.006</v>
+        <v>0.0069</v>
       </c>
       <c r="L62" s="29" t="n">
         <v>15972.4474</v>
@@ -16152,7 +16152,7 @@
         </is>
       </c>
       <c r="C63" s="24" t="n">
-        <v>218.879</v>
+        <v>219.54</v>
       </c>
       <c r="D63" s="22" t="inlineStr">
         <is>
@@ -16169,10 +16169,10 @@
         <v>52.6095</v>
       </c>
       <c r="H63" s="24" t="n">
-        <v>68.6211</v>
+        <v>68.621</v>
       </c>
       <c r="I63" s="24" t="n">
-        <v>68.6211</v>
+        <v>68.621</v>
       </c>
       <c r="J63" s="26" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         </is>
       </c>
       <c r="K63" s="24" t="n">
-        <v>4.7845</v>
+        <v>4.799</v>
       </c>
       <c r="L63" s="24" t="n">
         <v>34.3105</v>
@@ -16198,7 +16198,7 @@
         </is>
       </c>
       <c r="C64" s="24" t="n">
-        <v>146.64</v>
+        <v>146.33</v>
       </c>
       <c r="D64" s="22" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         </is>
       </c>
       <c r="K64" s="24" t="n">
-        <v>7.2513</v>
+        <v>7.2359</v>
       </c>
       <c r="L64" s="24" t="n">
         <v>15.167</v>
@@ -16244,7 +16244,7 @@
         </is>
       </c>
       <c r="C65" s="24" t="n">
-        <v>33.21</v>
+        <v>32.975</v>
       </c>
       <c r="D65" s="22" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         </is>
       </c>
       <c r="K65" s="24" t="n">
-        <v>7.614</v>
+        <v>7.5601</v>
       </c>
       <c r="L65" s="24" t="n">
         <v>3.2713</v>
@@ -16290,7 +16290,7 @@
         </is>
       </c>
       <c r="C66" s="24" t="n">
-        <v>365</v>
+        <v>365.1</v>
       </c>
       <c r="D66" s="22" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         </is>
       </c>
       <c r="K66" s="24" t="n">
-        <v>80.5956</v>
+        <v>80.6177</v>
       </c>
       <c r="L66" s="24" t="n">
         <v>3.3966</v>
@@ -16336,7 +16336,7 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>425.19</v>
+        <v>431.57</v>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
@@ -16344,19 +16344,19 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>3132.6577</v>
+        <v>3132.655</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>4698.9865</v>
+        <v>4698.9825</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>7205.1127</v>
+        <v>7205.1065</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>9397.973099999999</v>
+        <v>9397.965099999999</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>9397.973099999999</v>
+        <v>9397.965099999999</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
@@ -16364,10 +16364,10 @@
         </is>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0.0679</v>
+        <v>0.0689</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>4698.9865</v>
+        <v>4698.9825</v>
       </c>
     </row>
     <row r="68">
@@ -16382,7 +16382,7 @@
         </is>
       </c>
       <c r="C68" s="14" t="n">
-        <v>377.275</v>
+        <v>373.955</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
@@ -16390,19 +16390,19 @@
         </is>
       </c>
       <c r="E68" s="14" t="n">
-        <v>184.7123</v>
+        <v>184.7126</v>
       </c>
       <c r="F68" s="14" t="n">
-        <v>277.0684</v>
+        <v>277.0689</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>424.8382</v>
+        <v>424.839</v>
       </c>
       <c r="H68" s="14" t="n">
-        <v>554.1368</v>
+        <v>554.1378</v>
       </c>
       <c r="I68" s="14" t="n">
-        <v>554.1368</v>
+        <v>554.1378</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
@@ -16410,10 +16410,10 @@
         </is>
       </c>
       <c r="K68" s="14" t="n">
-        <v>1.0213</v>
+        <v>1.0123</v>
       </c>
       <c r="L68" s="14" t="n">
-        <v>277.0684</v>
+        <v>277.0689</v>
       </c>
     </row>
     <row r="69">
@@ -16428,7 +16428,7 @@
         </is>
       </c>
       <c r="C69" s="24" t="n">
-        <v>369.365</v>
+        <v>369.03</v>
       </c>
       <c r="D69" s="22" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         </is>
       </c>
       <c r="K69" s="24" t="n">
-        <v>6.8074</v>
+        <v>6.8012</v>
       </c>
       <c r="L69" s="24" t="n">
         <v>40.6947</v>
@@ -16474,7 +16474,7 @@
         </is>
       </c>
       <c r="C70" s="24" t="n">
-        <v>106.36</v>
+        <v>107.11</v>
       </c>
       <c r="D70" s="22" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         </is>
       </c>
       <c r="K70" s="24" t="n">
-        <v>8.9895</v>
+        <v>9.052899999999999</v>
       </c>
       <c r="L70" s="24" t="n">
         <v>8.873699999999999</v>
@@ -21461,7 +21461,7 @@
         </is>
       </c>
       <c r="C52" s="34" t="n">
-        <v>332.29</v>
+        <v>334.815</v>
       </c>
       <c r="D52" s="32" t="n">
         <v>152198000000</v>
@@ -21547,7 +21547,7 @@
         </is>
       </c>
       <c r="C53" s="34" t="n">
-        <v>252.07</v>
+        <v>253.56</v>
       </c>
       <c r="D53" s="32" t="n">
         <v>90623000000</v>
@@ -21635,7 +21635,7 @@
         </is>
       </c>
       <c r="C54" s="34" t="n">
-        <v>510.14</v>
+        <v>508.34</v>
       </c>
       <c r="D54" s="32" t="inlineStr"/>
       <c r="E54" s="32" t="n">
@@ -21707,7 +21707,7 @@
         </is>
       </c>
       <c r="C55" s="34" t="n">
-        <v>280.37</v>
+        <v>283.66</v>
       </c>
       <c r="D55" s="32" t="n">
         <v>1749124000</v>
@@ -21793,7 +21793,7 @@
         </is>
       </c>
       <c r="C56" s="34" t="n">
-        <v>174.765</v>
+        <v>167.445</v>
       </c>
       <c r="D56" s="32" t="n">
         <v>2322900000</v>
@@ -21879,7 +21879,7 @@
         </is>
       </c>
       <c r="C57" s="34" t="n">
-        <v>346.365</v>
+        <v>350.165</v>
       </c>
       <c r="D57" s="32" t="n">
         <v>137196000000</v>
@@ -21967,7 +21967,7 @@
         </is>
       </c>
       <c r="C58" s="34" t="n">
-        <v>269.25</v>
+        <v>268.515</v>
       </c>
       <c r="D58" s="32" t="n">
         <v>31538000000</v>
@@ -22051,7 +22051,7 @@
         </is>
       </c>
       <c r="C59" s="34" t="n">
-        <v>87.66500000000001</v>
+        <v>87.78</v>
       </c>
       <c r="D59" s="32" t="n">
         <v>13046000000</v>
@@ -22139,7 +22139,7 @@
         </is>
       </c>
       <c r="C60" s="34" t="n">
-        <v>1143.93</v>
+        <v>1146.22</v>
       </c>
       <c r="D60" s="32" t="n">
         <v>26708000000</v>
@@ -22225,7 +22225,7 @@
         </is>
       </c>
       <c r="C61" s="34" t="n">
-        <v>495.94</v>
+        <v>493.811</v>
       </c>
       <c r="D61" s="32" t="n">
         <v>90007000000</v>
@@ -22311,7 +22311,7 @@
         </is>
       </c>
       <c r="C62" s="34" t="n">
-        <v>128.7</v>
+        <v>147.92</v>
       </c>
       <c r="D62" s="32" t="n">
         <v>130869000</v>
@@ -22397,7 +22397,7 @@
         </is>
       </c>
       <c r="C63" s="34" t="n">
-        <v>218.879</v>
+        <v>219.54</v>
       </c>
       <c r="D63" s="32" t="n">
         <v>160482000000</v>
@@ -22485,7 +22485,7 @@
         </is>
       </c>
       <c r="C64" s="34" t="n">
-        <v>146.64</v>
+        <v>146.33</v>
       </c>
       <c r="D64" s="32" t="n">
         <v>21203000000</v>
@@ -22571,7 +22571,7 @@
         </is>
       </c>
       <c r="C65" s="34" t="n">
-        <v>33.21</v>
+        <v>32.975</v>
       </c>
       <c r="D65" s="32" t="n">
         <v>991962000</v>
@@ -22659,7 +22659,7 @@
         </is>
       </c>
       <c r="C66" s="34" t="n">
-        <v>365</v>
+        <v>365.1</v>
       </c>
       <c r="D66" s="32" t="n">
         <v>30641000000</v>
@@ -22747,7 +22747,7 @@
         </is>
       </c>
       <c r="C67" s="34" t="n">
-        <v>425.19</v>
+        <v>431.57</v>
       </c>
       <c r="D67" s="32" t="n">
         <v>1382678381000</v>
@@ -22835,7 +22835,7 @@
         </is>
       </c>
       <c r="C68" s="34" t="n">
-        <v>377.275</v>
+        <v>373.955</v>
       </c>
       <c r="D68" s="32" t="n">
         <v>113631000000</v>
@@ -22921,7 +22921,7 @@
         </is>
       </c>
       <c r="C69" s="34" t="n">
-        <v>369.365</v>
+        <v>369.03</v>
       </c>
       <c r="D69" s="32" t="n">
         <v>12362000000</v>
@@ -23007,7 +23007,7 @@
         </is>
       </c>
       <c r="C70" s="34" t="n">
-        <v>106.36</v>
+        <v>107.11</v>
       </c>
       <c r="D70" s="32" t="n">
         <v>201191000000</v>
@@ -26240,7 +26240,7 @@
         </is>
       </c>
       <c r="C52" s="24" t="n">
-        <v>332.29</v>
+        <v>334.815</v>
       </c>
       <c r="D52" s="22" t="n">
         <v>3</v>
@@ -26301,7 +26301,7 @@
         </is>
       </c>
       <c r="C53" s="24" t="n">
-        <v>252.07</v>
+        <v>253.56</v>
       </c>
       <c r="D53" s="22" t="n">
         <v>2.3</v>
@@ -26362,7 +26362,7 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>510.14</v>
+        <v>508.34</v>
       </c>
       <c r="D54" s="2" t="n">
         <v>5.5</v>
@@ -26423,7 +26423,7 @@
         </is>
       </c>
       <c r="C55" s="24" t="n">
-        <v>280.37</v>
+        <v>283.66</v>
       </c>
       <c r="D55" s="22" t="n">
         <v>2</v>
@@ -26484,7 +26484,7 @@
         </is>
       </c>
       <c r="C56" s="24" t="n">
-        <v>174.765</v>
+        <v>167.445</v>
       </c>
       <c r="D56" s="22" t="n">
         <v>3</v>
@@ -26545,7 +26545,7 @@
         </is>
       </c>
       <c r="C57" s="24" t="n">
-        <v>346.365</v>
+        <v>350.165</v>
       </c>
       <c r="D57" s="22" t="n">
         <v>2.3</v>
@@ -26606,7 +26606,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>269.25</v>
+        <v>268.515</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>3.5</v>
@@ -26667,7 +26667,7 @@
         </is>
       </c>
       <c r="C59" s="24" t="n">
-        <v>87.66500000000001</v>
+        <v>87.78</v>
       </c>
       <c r="D59" s="22" t="n">
         <v>2</v>
@@ -26728,7 +26728,7 @@
         </is>
       </c>
       <c r="C60" s="24" t="n">
-        <v>1143.93</v>
+        <v>1146.22</v>
       </c>
       <c r="D60" s="22" t="n">
         <v>2.5</v>
@@ -26789,7 +26789,7 @@
         </is>
       </c>
       <c r="C61" s="24" t="n">
-        <v>495.94</v>
+        <v>493.811</v>
       </c>
       <c r="D61" s="22" t="n">
         <v>2.8</v>
@@ -26850,7 +26850,7 @@
         </is>
       </c>
       <c r="C62" s="29" t="n">
-        <v>128.7</v>
+        <v>147.92</v>
       </c>
       <c r="D62" s="27" t="n">
         <v>1</v>
@@ -26911,7 +26911,7 @@
         </is>
       </c>
       <c r="C63" s="24" t="n">
-        <v>218.879</v>
+        <v>219.54</v>
       </c>
       <c r="D63" s="22" t="n">
         <v>3.5</v>
@@ -26972,7 +26972,7 @@
         </is>
       </c>
       <c r="C64" s="24" t="n">
-        <v>146.64</v>
+        <v>146.33</v>
       </c>
       <c r="D64" s="22" t="n">
         <v>2</v>
@@ -27033,7 +27033,7 @@
         </is>
       </c>
       <c r="C65" s="24" t="n">
-        <v>33.21</v>
+        <v>32.975</v>
       </c>
       <c r="D65" s="22" t="n">
         <v>2.3</v>
@@ -27094,7 +27094,7 @@
         </is>
       </c>
       <c r="C66" s="24" t="n">
-        <v>365</v>
+        <v>365.1</v>
       </c>
       <c r="D66" s="22" t="n">
         <v>1.2</v>
@@ -27155,7 +27155,7 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>425.19</v>
+        <v>431.57</v>
       </c>
       <c r="D67" s="2" t="n">
         <v>7.5</v>
@@ -27216,7 +27216,7 @@
         </is>
       </c>
       <c r="C68" s="14" t="n">
-        <v>377.275</v>
+        <v>373.955</v>
       </c>
       <c r="D68" s="12" t="n">
         <v>2.5</v>
@@ -27277,7 +27277,7 @@
         </is>
       </c>
       <c r="C69" s="24" t="n">
-        <v>369.365</v>
+        <v>369.03</v>
       </c>
       <c r="D69" s="22" t="n">
         <v>2.5</v>
@@ -27338,7 +27338,7 @@
         </is>
       </c>
       <c r="C70" s="24" t="n">
-        <v>106.36</v>
+        <v>107.11</v>
       </c>
       <c r="D70" s="22" t="n">
         <v>2.2</v>
